--- a/data/trans_orig/P21_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>62908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>95935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55868</t>
+          <t>54583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84037</t>
+          <t>83860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125537</t>
+          <t>125732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168343</t>
+          <t>170481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377286</t>
+          <t>377841</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409882</t>
+          <t>410868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222643</t>
+          <t>222820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250812</t>
+          <t>252097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612114</t>
+          <t>609976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>654920</t>
+          <t>654725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83893</t>
+          <t>84707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>75974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107926</t>
+          <t>107330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136030</t>
+          <t>136247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179916</t>
+          <t>180954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282156</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313768</t>
+          <t>314624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262998</t>
+          <t>263594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296816</t>
+          <t>294950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>557058</t>
+          <t>556020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600944</t>
+          <t>600727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79406</t>
+          <t>79039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115067</t>
+          <t>113484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36605</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59756</t>
+          <t>60125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123424</t>
+          <t>123092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164595</t>
+          <t>166410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427322</t>
+          <t>428905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462983</t>
+          <t>463350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108026</t>
+          <t>107657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131177</t>
+          <t>131768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545576</t>
+          <t>543761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>586747</t>
+          <t>587079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197955</t>
+          <t>194927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253659</t>
+          <t>252576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163481</t>
+          <t>166917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210389</t>
+          <t>212377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381793</t>
+          <t>377644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>452256</t>
+          <t>449696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>984675</t>
+          <t>985758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1040379</t>
+          <t>1043407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>503896</t>
+          <t>501908</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>550804</t>
+          <t>547368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1500364</t>
+          <t>1502924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1570827</t>
+          <t>1574976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63462</t>
+          <t>63367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118302</t>
+          <t>115219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160226</t>
+          <t>157761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160413</t>
+          <t>161395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210909</t>
+          <t>212514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287093</t>
+          <t>287188</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>313956</t>
+          <t>313061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408526</t>
+          <t>410991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>450450</t>
+          <t>453533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708398</t>
+          <t>706793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>758894</t>
+          <t>757912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>34009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57765</t>
+          <t>58034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>262306</t>
+          <t>261557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>321050</t>
+          <t>323225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>306740</t>
+          <t>305857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>370392</t>
+          <t>368898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240436</t>
+          <t>240167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264652</t>
+          <t>264192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>927710</t>
+          <t>925535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>986454</t>
+          <t>987203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1176568</t>
+          <t>1178062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1240220</t>
+          <t>1241103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>516913</t>
+          <t>516543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>605255</t>
+          <t>601889</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>774485</t>
+          <t>777477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>874519</t>
+          <t>877502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1324397</t>
+          <t>1315957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1453579</t>
+          <t>1450120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2664050</t>
+          <t>2667416</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2752392</t>
+          <t>2752762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2502665</t>
+          <t>2499682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2602699</t>
+          <t>2599707</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5192910</t>
+          <t>5196369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5322092</t>
+          <t>5330532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71212</t>
+          <t>72457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>64172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99833</t>
+          <t>99489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114543</t>
+          <t>116076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159009</t>
+          <t>158854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365999</t>
+          <t>364754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394872</t>
+          <t>396238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214621</t>
+          <t>214965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248372</t>
+          <t>250282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592656</t>
+          <t>592811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>637122</t>
+          <t>635589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56200</t>
+          <t>56084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88491</t>
+          <t>89061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>70456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103384</t>
+          <t>104820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135899</t>
+          <t>135678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182654</t>
+          <t>185832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330306</t>
+          <t>329736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362597</t>
+          <t>362713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232480</t>
+          <t>231044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>264632</t>
+          <t>265408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>572007</t>
+          <t>568829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618762</t>
+          <t>618983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134403</t>
+          <t>134739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180146</t>
+          <t>181996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184930</t>
+          <t>184619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237079</t>
+          <t>238132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448315</t>
+          <t>446465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494058</t>
+          <t>493722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191677</t>
+          <t>194047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217924</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651511</t>
+          <t>650458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703660</t>
+          <t>703971</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229089</t>
+          <t>225309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>286145</t>
+          <t>285158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197615</t>
+          <t>195539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250363</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438598</t>
+          <t>435065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514974</t>
+          <t>514960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871138</t>
+          <t>872125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>928194</t>
+          <t>931974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>516294</t>
+          <t>518962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569042</t>
+          <t>571118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1408966</t>
+          <t>1408980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1485342</t>
+          <t>1488875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90141</t>
+          <t>91476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128747</t>
+          <t>128322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208461</t>
+          <t>206862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257352</t>
+          <t>259067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308895</t>
+          <t>307992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373467</t>
+          <t>374825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>382274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420455</t>
+          <t>419120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>503211</t>
+          <t>501496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>552102</t>
+          <t>553701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>897692</t>
+          <t>896334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>962264</t>
+          <t>963167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>76178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>269913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>332104</t>
+          <t>331840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>332697</t>
+          <t>330540</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>396794</t>
+          <t>399632</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192443</t>
+          <t>190704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220378</t>
+          <t>219435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>777247</t>
+          <t>777511</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>838432</t>
+          <t>839438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>979439</t>
+          <t>976601</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1043536</t>
+          <t>1045693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>660780</t>
+          <t>657648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>757479</t>
+          <t>756041</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>919661</t>
+          <t>927565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1029957</t>
+          <t>1032851</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1619811</t>
+          <t>1609170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1765827</t>
+          <t>1761056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2661750</t>
+          <t>2663188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2758449</t>
+          <t>2761581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2517063</t>
+          <t>2514169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2627359</t>
+          <t>2619455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5200422</t>
+          <t>5205193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5346438</t>
+          <t>5357079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48837</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80174</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>61970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91974</t>
+          <t>93916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118149</t>
+          <t>120389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>162139</t>
+          <t>163468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348918</t>
+          <t>347394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380255</t>
+          <t>379611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252394</t>
+          <t>250452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282096</t>
+          <t>282398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>611321</t>
+          <t>609992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655311</t>
+          <t>653071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42580</t>
+          <t>41689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70517</t>
+          <t>70493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66162</t>
+          <t>65610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98241</t>
+          <t>98530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117463</t>
+          <t>117007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160258</t>
+          <t>159082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304783</t>
+          <t>304807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332720</t>
+          <t>333611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>273148</t>
+          <t>272859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305227</t>
+          <t>305779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>586431</t>
+          <t>587607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629226</t>
+          <t>629682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72072</t>
+          <t>72659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109229</t>
+          <t>109130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>42330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102834</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142902</t>
+          <t>143238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412685</t>
+          <t>412784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449842</t>
+          <t>449255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122014</t>
+          <t>122176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543518</t>
+          <t>543182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>583586</t>
+          <t>584265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164501</t>
+          <t>167390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217333</t>
+          <t>216964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175556</t>
+          <t>175231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224310</t>
+          <t>226825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>358467</t>
+          <t>356407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>429444</t>
+          <t>426942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927723</t>
+          <t>928092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>980555</t>
+          <t>977666</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601566</t>
+          <t>599051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>650320</t>
+          <t>650645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1541488</t>
+          <t>1543990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1612465</t>
+          <t>1614525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80655</t>
+          <t>83848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118195</t>
+          <t>119440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130761</t>
+          <t>129454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176273</t>
+          <t>176819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222097</t>
+          <t>222043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281305</t>
+          <t>282698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498355</t>
+          <t>497110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535895</t>
+          <t>532702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561971</t>
+          <t>561425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>607483</t>
+          <t>608790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1073489</t>
+          <t>1072096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1132697</t>
+          <t>1132751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51160</t>
+          <t>50829</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79037</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194572</t>
+          <t>191228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>250209</t>
+          <t>247458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>251850</t>
+          <t>255039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>312911</t>
+          <t>315055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208108</t>
+          <t>207268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235985</t>
+          <t>236316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>830545</t>
+          <t>833296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>886182</t>
+          <t>889526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1054988</t>
+          <t>1052844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1116049</t>
+          <t>1112860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>520388</t>
+          <t>521097</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>609780</t>
+          <t>609603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>708126</t>
+          <t>715706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>810484</t>
+          <t>812666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1261081</t>
+          <t>1259392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1399464</t>
+          <t>1393235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2765276</t>
+          <t>2765453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2854668</t>
+          <t>2853959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2714653</t>
+          <t>2712471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2817011</t>
+          <t>2809431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5500729</t>
+          <t>5506958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5639112</t>
+          <t>5640801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102050</t>
+          <t>103133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144254</t>
+          <t>146349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93432</t>
+          <t>94591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124996</t>
+          <t>124911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204801</t>
+          <t>207196</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258791</t>
+          <t>258632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359205</t>
+          <t>357110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401409</t>
+          <t>400326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321754</t>
+          <t>321839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353318</t>
+          <t>352159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691418</t>
+          <t>691577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745408</t>
+          <t>743013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>62255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95128</t>
+          <t>94892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>85753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115316</t>
+          <t>115389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153976</t>
+          <t>154172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200667</t>
+          <t>197036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357085</t>
+          <t>357321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389034</t>
+          <t>389958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266389</t>
+          <t>266316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296467</t>
+          <t>295952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633250</t>
+          <t>636881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679941</t>
+          <t>679745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31394</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145174</t>
+          <t>147739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62949</t>
+          <t>63181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>55430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208660</t>
+          <t>205984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523090</t>
+          <t>520525</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636870</t>
+          <t>634568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103311</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123190</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625864</t>
+          <t>628540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>771380</t>
+          <t>779094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198201</t>
+          <t>199035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258311</t>
+          <t>259995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>268403</t>
+          <t>265903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>695838</t>
+          <t>643840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>480168</t>
+          <t>482565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033751</t>
+          <t>1092193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776508</t>
+          <t>774824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>836618</t>
+          <t>835784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>334254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709691</t>
+          <t>712191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>979161</t>
+          <t>920719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1532744</t>
+          <t>1530347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80273</t>
+          <t>81043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>118085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131890</t>
+          <t>131662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206636</t>
+          <t>207142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224937</t>
+          <t>227509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>305884</t>
+          <t>307866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>358085</t>
+          <t>356961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>394773</t>
+          <t>394003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631814</t>
+          <t>631308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706560</t>
+          <t>706788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1007612</t>
+          <t>1005630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1088559</t>
+          <t>1085987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29611</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141141</t>
+          <t>140136</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>184979</t>
+          <t>180607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181733</t>
+          <t>179437</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240166</t>
+          <t>243013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171004</t>
+          <t>167404</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210896</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>573633</t>
+          <t>578005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>617471</t>
+          <t>618476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>758954</t>
+          <t>756107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>817387</t>
+          <t>819683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>521695</t>
+          <t>519947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>730731</t>
+          <t>726450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>846380</t>
+          <t>846844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1565380</t>
+          <t>1532269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1467421</t>
+          <t>1466024</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2298363</t>
+          <t>2258019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2643576</t>
+          <t>2647857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2852612</t>
+          <t>2854360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2004491</t>
+          <t>2037602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2723491</t>
+          <t>2723027</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4645815</t>
+          <t>4686159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5476757</t>
+          <t>5478154</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62908</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95935</t>
+          <t>96379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54583</t>
+          <t>54230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83860</t>
+          <t>83837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125732</t>
+          <t>123627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170481</t>
+          <t>168315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>377397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410868</t>
+          <t>412130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222820</t>
+          <t>222843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252097</t>
+          <t>252450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609976</t>
+          <t>612142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>654725</t>
+          <t>656830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>52165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>82680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75974</t>
+          <t>73989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107330</t>
+          <t>107856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136247</t>
+          <t>136950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180954</t>
+          <t>183654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>283369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314624</t>
+          <t>313884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263594</t>
+          <t>263068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294950</t>
+          <t>296935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>556020</t>
+          <t>553320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600727</t>
+          <t>600024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79039</t>
+          <t>81051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113484</t>
+          <t>115214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>35248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>58370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123092</t>
+          <t>122565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166410</t>
+          <t>165860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>428905</t>
+          <t>427175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463350</t>
+          <t>461338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107657</t>
+          <t>109412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131768</t>
+          <t>132534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543761</t>
+          <t>544311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>587079</t>
+          <t>587606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194927</t>
+          <t>198359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>252576</t>
+          <t>253591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166917</t>
+          <t>167479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>212881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377644</t>
+          <t>379988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>449696</t>
+          <t>450543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>985758</t>
+          <t>984743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1043407</t>
+          <t>1039975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501908</t>
+          <t>501404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>547368</t>
+          <t>546806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502924</t>
+          <t>1502077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1574976</t>
+          <t>1572632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>35538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>62653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115219</t>
+          <t>114869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157761</t>
+          <t>158899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161395</t>
+          <t>162194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212514</t>
+          <t>210936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287188</t>
+          <t>287902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>313061</t>
+          <t>315017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>410991</t>
+          <t>409853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>453533</t>
+          <t>453883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706793</t>
+          <t>708371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>757912</t>
+          <t>757113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34009</t>
+          <t>32283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58034</t>
+          <t>57632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>261557</t>
+          <t>262066</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>323225</t>
+          <t>320459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>305857</t>
+          <t>304824</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>368898</t>
+          <t>367358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240167</t>
+          <t>240569</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264192</t>
+          <t>265918</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>925535</t>
+          <t>928301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>987203</t>
+          <t>986694</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1178062</t>
+          <t>1179602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1241103</t>
+          <t>1242136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>516543</t>
+          <t>517748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>601889</t>
+          <t>600711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>777477</t>
+          <t>773754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>877502</t>
+          <t>869712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1315957</t>
+          <t>1316353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1450120</t>
+          <t>1452249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2667416</t>
+          <t>2668594</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2752762</t>
+          <t>2751557</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2499682</t>
+          <t>2507472</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2599707</t>
+          <t>2603430</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5196369</t>
+          <t>5194240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5330532</t>
+          <t>5330136</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>41529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>70829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64172</t>
+          <t>64337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99489</t>
+          <t>98853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116076</t>
+          <t>113987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158854</t>
+          <t>159433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364754</t>
+          <t>366382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396238</t>
+          <t>395682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214965</t>
+          <t>215601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250282</t>
+          <t>250117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592811</t>
+          <t>592232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635589</t>
+          <t>637678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56084</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89061</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>69464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104820</t>
+          <t>103714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135678</t>
+          <t>135120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185832</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329736</t>
+          <t>329691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362713</t>
+          <t>362536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231044</t>
+          <t>232150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>265408</t>
+          <t>266400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568829</t>
+          <t>572332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618983</t>
+          <t>619541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181996</t>
+          <t>180351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39783</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184619</t>
+          <t>185522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238132</t>
+          <t>235820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446465</t>
+          <t>448110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493722</t>
+          <t>494511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>192556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>219059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650458</t>
+          <t>652770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703971</t>
+          <t>703068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225309</t>
+          <t>225734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>285158</t>
+          <t>283899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195539</t>
+          <t>196241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>245535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435065</t>
+          <t>438534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514960</t>
+          <t>518097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872125</t>
+          <t>873384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931974</t>
+          <t>931549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>518962</t>
+          <t>521122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>571118</t>
+          <t>570416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1408980</t>
+          <t>1405843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1488875</t>
+          <t>1485406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91476</t>
+          <t>92840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128322</t>
+          <t>127345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>206862</t>
+          <t>204909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259067</t>
+          <t>258423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307992</t>
+          <t>311029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374825</t>
+          <t>375970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>382274</t>
+          <t>383251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419120</t>
+          <t>417756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>501496</t>
+          <t>502140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>553701</t>
+          <t>555654</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>896334</t>
+          <t>895189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963167</t>
+          <t>960130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47447</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>73663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269913</t>
+          <t>273543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>331840</t>
+          <t>336623</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>330540</t>
+          <t>328591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>399632</t>
+          <t>395883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190704</t>
+          <t>193219</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219435</t>
+          <t>219553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>777511</t>
+          <t>772728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>839438</t>
+          <t>835808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>976601</t>
+          <t>980350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1045693</t>
+          <t>1047642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>657648</t>
+          <t>658747</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>756041</t>
+          <t>757603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>927565</t>
+          <t>926457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1032851</t>
+          <t>1035071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1609170</t>
+          <t>1619180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1761056</t>
+          <t>1760012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2663188</t>
+          <t>2661626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2761581</t>
+          <t>2760482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2514169</t>
+          <t>2511949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2619455</t>
+          <t>2620563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5205193</t>
+          <t>5206237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5357079</t>
+          <t>5347069</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49481</t>
+          <t>48823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81698</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61970</t>
+          <t>60907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93916</t>
+          <t>92396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120389</t>
+          <t>120015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163468</t>
+          <t>163869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347394</t>
+          <t>348602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379611</t>
+          <t>380269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250452</t>
+          <t>251972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282398</t>
+          <t>283461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609992</t>
+          <t>609591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>653071</t>
+          <t>653445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41689</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>71704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65610</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98530</t>
+          <t>101248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117007</t>
+          <t>118601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159082</t>
+          <t>160764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304807</t>
+          <t>303596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333611</t>
+          <t>332983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272859</t>
+          <t>270141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305779</t>
+          <t>303749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>587607</t>
+          <t>585925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629682</t>
+          <t>628088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72659</t>
+          <t>73717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109130</t>
+          <t>109561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>22971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42330</t>
+          <t>42892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>101342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143238</t>
+          <t>140636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412784</t>
+          <t>412353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449255</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122176</t>
+          <t>121614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142322</t>
+          <t>141535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543182</t>
+          <t>545784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584265</t>
+          <t>585078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167390</t>
+          <t>166320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>216964</t>
+          <t>218564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175231</t>
+          <t>177652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>226825</t>
+          <t>227911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>356407</t>
+          <t>358028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>426942</t>
+          <t>430932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928092</t>
+          <t>926492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>977666</t>
+          <t>978736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599051</t>
+          <t>597965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>650645</t>
+          <t>648224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1543990</t>
+          <t>1540000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1614525</t>
+          <t>1612904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119440</t>
+          <t>121073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129454</t>
+          <t>128499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176819</t>
+          <t>173576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222043</t>
+          <t>221913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282698</t>
+          <t>282818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497110</t>
+          <t>495477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532702</t>
+          <t>533700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561425</t>
+          <t>564668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>608790</t>
+          <t>609745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072096</t>
+          <t>1071976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1132751</t>
+          <t>1132881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>78531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191228</t>
+          <t>193576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247458</t>
+          <t>245259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>252069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>315055</t>
+          <t>316785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207268</t>
+          <t>208614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236316</t>
+          <t>238510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>833296</t>
+          <t>835495</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>889526</t>
+          <t>887178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1052844</t>
+          <t>1051114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1112860</t>
+          <t>1115830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>521097</t>
+          <t>521939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>609603</t>
+          <t>610208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>715706</t>
+          <t>710985</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>812666</t>
+          <t>814941</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1259392</t>
+          <t>1260983</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1393235</t>
+          <t>1398261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2765453</t>
+          <t>2764848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2853959</t>
+          <t>2853117</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2712471</t>
+          <t>2710196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2809431</t>
+          <t>2814152</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5506958</t>
+          <t>5501932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5640801</t>
+          <t>5639210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>121437</t>
+          <t>130751</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103133</t>
+          <t>111448</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146349</t>
+          <t>154512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>109067</t>
+          <t>117961</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94591</t>
+          <t>101126</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124911</t>
+          <t>133554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>230503</t>
+          <t>248712</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207196</t>
+          <t>222850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258632</t>
+          <t>277152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>382022</t>
+          <t>417897</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357110</t>
+          <t>394136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400326</t>
+          <t>437200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>337683</t>
+          <t>369702</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321839</t>
+          <t>354109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>352159</t>
+          <t>386537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>719706</t>
+          <t>787598</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691577</t>
+          <t>759158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743013</t>
+          <t>813460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>548648</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>548648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>548648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446750</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446750</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446750</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1036310</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1036310</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1036310</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>82222</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62255</t>
+          <t>66289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98799</t>
+          <t>109159</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85753</t>
+          <t>93720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115389</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>176332</t>
+          <t>191382</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154172</t>
+          <t>169574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197036</t>
+          <t>217656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374680</t>
+          <t>400990</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357321</t>
+          <t>382087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389958</t>
+          <t>416923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>282906</t>
+          <t>313111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266316</t>
+          <t>295104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295952</t>
+          <t>328550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>657585</t>
+          <t>714100</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>636881</t>
+          <t>687826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679745</t>
+          <t>735908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,27%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87537</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147739</t>
+          <t>116575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,22 +9354,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52277</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>71194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>139814</t>
+          <t>155558</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>136797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205984</t>
+          <t>178600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>580727</t>
+          <t>374885</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520525</t>
+          <t>355037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634568</t>
+          <t>392821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,27 +9467,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113983</t>
+          <t>127973</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103079</t>
+          <t>115611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>138257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>694710</t>
+          <t>502858</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628540</t>
+          <t>479816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>779094</t>
+          <t>521619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166260</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166260</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166260</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>658416</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>658416</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>658416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>226630</t>
+          <t>250508</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199035</t>
+          <t>221692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259995</t>
+          <t>283345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>422536</t>
+          <t>245298</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>265903</t>
+          <t>221888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>643840</t>
+          <t>269360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>649166</t>
+          <t>495806</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482565</t>
+          <t>462000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1092193</t>
+          <t>536734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>808189</t>
+          <t>881335</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>774824</t>
+          <t>848498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>835784</t>
+          <t>910151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>555558</t>
+          <t>615913</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334254</t>
+          <t>591851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>712191</t>
+          <t>639323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1363746</t>
+          <t>1497248</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>920719</t>
+          <t>1456320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1530347</t>
+          <t>1531054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>109341</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81043</t>
+          <t>91337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118085</t>
+          <t>132390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>177207</t>
+          <t>199245</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131662</t>
+          <t>180457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207142</t>
+          <t>222120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>273751</t>
+          <t>308586</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227509</t>
+          <t>281830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307866</t>
+          <t>339469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>378502</t>
+          <t>458623</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>356961</t>
+          <t>435574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>394003</t>
+          <t>476627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>661243</t>
+          <t>630338</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631308</t>
+          <t>607463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706788</t>
+          <t>649126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1039745</t>
+          <t>1088960</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1005630</t>
+          <t>1058077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1085987</t>
+          <t>1115716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838450</t>
+          <t>829583</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838450</t>
+          <t>829583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838450</t>
+          <t>829583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313496</t>
+          <t>1397546</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313496</t>
+          <t>1397546</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313496</t>
+          <t>1397546</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73103</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>160892</t>
+          <t>175211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>140136</t>
+          <t>154652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180607</t>
+          <t>199223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>206955</t>
+          <t>217589</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179437</t>
+          <t>187955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243013</t>
+          <t>248650</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>194444</t>
+          <t>194851</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167404</t>
+          <t>173801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211535</t>
+          <t>210418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>597720</t>
+          <t>666253</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>578005</t>
+          <t>642241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>618476</t>
+          <t>686812</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>792165</t>
+          <t>861103</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>756107</t>
+          <t>830042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>819683</t>
+          <t>890737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>841464</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>841464</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>841464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999120</t>
+          <t>1078692</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999120</t>
+          <t>1078692</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999120</t>
+          <t>1078692</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>655743</t>
+          <t>711926</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>519947</t>
+          <t>661699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>726450</t>
+          <t>765084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1020778</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>846844</t>
+          <t>860473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1532269</t>
+          <t>953746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1676522</t>
+          <t>1617633</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1466024</t>
+          <t>1551853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2258019</t>
+          <t>1693385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2718564</t>
+          <t>2728579</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2647857</t>
+          <t>2675421</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2854360</t>
+          <t>2778806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2549093</t>
+          <t>2723289</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2037602</t>
+          <t>2675250</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2723027</t>
+          <t>2768523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5267656</t>
+          <t>5451869</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4686159</t>
+          <t>5376117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5478154</t>
+          <t>5517649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374307</t>
+          <t>3440505</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374307</t>
+          <t>3440505</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374307</t>
+          <t>3440505</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3569871</t>
+          <t>3628996</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3569871</t>
+          <t>3628996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3569871</t>
+          <t>3628996</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944178</t>
+          <t>7069502</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944178</t>
+          <t>7069502</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944178</t>
+          <t>7069502</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
